--- a/Test cases/Casus 2 - Infeasible/Timetable Casus 2.xlsx
+++ b/Test cases/Casus 2 - Infeasible/Timetable Casus 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/872575_fontys_nl/Documents/Documenten/Python/PJ5 Dataset/Casus 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Test cases/Casus 2 - Infeasible/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_085DC7CF9342980E6235547658DFFEBCAC5D9814" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC191A2D-9DE6-4D7E-84AD-D45D66363EC1}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_085DC7CF9342980E6235547658DFFEBCAC5D9814" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AA063E0-E2B5-427A-8DB9-C308C75F5AC0}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
   <si>
-    <t>start location</t>
-  </si>
-  <si>
-    <t>start time</t>
-  </si>
-  <si>
     <t>end</t>
   </si>
   <si>
@@ -122,6 +116,12 @@
   </si>
   <si>
     <t>16:51</t>
+  </si>
+  <si>
+    <t>departure_time</t>
+  </si>
+  <si>
+    <t>start</t>
   </si>
 </sst>
 </file>
@@ -140,6 +140,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,7 +185,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -489,27 +490,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>400</v>
@@ -517,13 +518,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>400</v>
@@ -531,13 +532,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>401</v>
@@ -545,13 +546,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>401</v>
@@ -559,13 +560,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>401</v>
@@ -573,13 +574,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>401</v>
@@ -587,13 +588,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>401</v>
@@ -601,13 +602,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>401</v>
@@ -615,13 +616,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>401</v>
@@ -629,13 +630,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11">
         <v>401</v>
@@ -643,13 +644,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <v>401</v>
@@ -657,13 +658,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <v>401</v>
@@ -671,13 +672,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14">
         <v>401</v>
@@ -685,13 +686,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15">
         <v>401</v>
@@ -699,13 +700,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16">
         <v>401</v>
@@ -713,13 +714,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>401</v>
@@ -727,13 +728,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <v>401</v>
@@ -741,13 +742,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>401</v>
@@ -755,13 +756,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20">
         <v>401</v>
@@ -769,13 +770,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21">
         <v>401</v>
@@ -783,13 +784,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22">
         <v>401</v>
@@ -797,13 +798,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>401</v>
@@ -811,13 +812,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>401</v>
@@ -825,13 +826,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>401</v>
@@ -839,13 +840,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26">
         <v>401</v>
@@ -853,13 +854,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>401</v>
@@ -867,13 +868,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>401</v>
@@ -881,13 +882,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>401</v>
